--- a/academias/Ciencias Sociales - Estadisticos 20231.xlsx
+++ b/academias/Ciencias Sociales - Estadisticos 20231.xlsx
@@ -687,22 +687,22 @@
         <v>30</v>
       </c>
       <c r="D5">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5">
         <v>3</v>
       </c>
       <c r="G5" s="1">
-        <v>91.2</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="H5" s="1">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="I5" s="2">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -722,22 +722,22 @@
         <v>31</v>
       </c>
       <c r="D6">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E6">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F6">
         <v>3</v>
       </c>
       <c r="G6" s="1">
-        <v>92.3</v>
+        <v>92.5</v>
       </c>
       <c r="H6" s="1">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="I6" s="2">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -792,19 +792,19 @@
         <v>33</v>
       </c>
       <c r="D8">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E8">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F8">
         <v>12</v>
       </c>
       <c r="G8" s="1">
-        <v>69.2</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="H8" s="1">
-        <v>30.8</v>
+        <v>31.6</v>
       </c>
       <c r="I8" s="2">
         <v>6.3</v>
@@ -824,10 +824,10 @@
         <v>25</v>
       </c>
       <c r="D9">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E9">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F9">
         <v>25</v>
@@ -839,7 +839,7 @@
         <v>14</v>
       </c>
       <c r="I9" s="2">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1165,19 +1165,19 @@
         <v>40</v>
       </c>
       <c r="D19">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E19">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F19">
         <v>14</v>
       </c>
       <c r="G19" s="1">
-        <v>65</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="H19" s="1">
-        <v>35</v>
+        <v>35.9</v>
       </c>
       <c r="I19" s="2">
         <v>5.9</v>
@@ -1197,19 +1197,19 @@
         <v>25</v>
       </c>
       <c r="D20">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E20">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F20">
         <v>14</v>
       </c>
       <c r="G20" s="1">
-        <v>65</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="H20" s="1">
-        <v>35</v>
+        <v>35.9</v>
       </c>
       <c r="I20" s="2">
         <v>5.9</v>
@@ -1570,13 +1570,13 @@
         <v>47</v>
       </c>
       <c r="D31">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E31">
         <v>0</v>
       </c>
       <c r="F31">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G31" s="1">
         <v>0</v>
@@ -1588,7 +1588,7 @@
         <v>0</v>
       </c>
       <c r="J31">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K31" s="1">
         <v>100</v>
@@ -1602,28 +1602,28 @@
         <v>25</v>
       </c>
       <c r="D32">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E32">
         <v>12</v>
       </c>
       <c r="F32">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G32" s="1">
-        <v>13.2</v>
+        <v>13</v>
       </c>
       <c r="H32" s="1">
-        <v>86.8</v>
+        <v>87</v>
       </c>
       <c r="I32" s="2">
         <v>2</v>
       </c>
       <c r="J32">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K32" s="1">
-        <v>61.5</v>
+        <v>62</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -1765,28 +1765,28 @@
         <v>27</v>
       </c>
       <c r="D37">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="E37">
         <v>462</v>
       </c>
       <c r="F37">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G37" s="1">
-        <v>69.3</v>
+        <v>69.2</v>
       </c>
       <c r="H37" s="1">
-        <v>30.7</v>
+        <v>30.8</v>
       </c>
       <c r="I37" s="2">
         <v>6.2</v>
       </c>
       <c r="J37">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K37" s="1">
-        <v>17.4</v>
+        <v>17.5</v>
       </c>
     </row>
   </sheetData>
@@ -1953,13 +1953,13 @@
         <v>30</v>
       </c>
       <c r="D5">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
@@ -1971,7 +1971,7 @@
         <v>0</v>
       </c>
       <c r="J5">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K5" s="1">
         <v>100</v>
@@ -1988,13 +1988,13 @@
         <v>31</v>
       </c>
       <c r="D6">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
@@ -2006,7 +2006,7 @@
         <v>0</v>
       </c>
       <c r="J6">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K6" s="1">
         <v>100</v>
@@ -2058,13 +2058,13 @@
         <v>33</v>
       </c>
       <c r="D8">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
@@ -2076,7 +2076,7 @@
         <v>0</v>
       </c>
       <c r="J8">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K8" s="1">
         <v>100</v>
@@ -2090,13 +2090,13 @@
         <v>25</v>
       </c>
       <c r="D9">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E9">
         <v>0</v>
       </c>
       <c r="F9">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
@@ -2108,7 +2108,7 @@
         <v>0</v>
       </c>
       <c r="J9">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="K9" s="1">
         <v>100</v>
@@ -2431,13 +2431,13 @@
         <v>40</v>
       </c>
       <c r="D19">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E19">
         <v>0</v>
       </c>
       <c r="F19">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G19" s="1">
         <v>0</v>
@@ -2449,7 +2449,7 @@
         <v>0</v>
       </c>
       <c r="J19">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K19" s="1">
         <v>100</v>
@@ -2463,13 +2463,13 @@
         <v>25</v>
       </c>
       <c r="D20">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E20">
         <v>0</v>
       </c>
       <c r="F20">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G20" s="1">
         <v>0</v>
@@ -2481,7 +2481,7 @@
         <v>0</v>
       </c>
       <c r="J20">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K20" s="1">
         <v>100</v>
@@ -2836,13 +2836,13 @@
         <v>47</v>
       </c>
       <c r="D31">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E31">
         <v>0</v>
       </c>
       <c r="F31">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G31" s="1">
         <v>0</v>
@@ -2854,7 +2854,7 @@
         <v>0</v>
       </c>
       <c r="J31">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K31" s="1">
         <v>100</v>
@@ -2868,13 +2868,13 @@
         <v>25</v>
       </c>
       <c r="D32">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E32">
         <v>0</v>
       </c>
       <c r="F32">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G32" s="1">
         <v>0</v>
@@ -2886,7 +2886,7 @@
         <v>0</v>
       </c>
       <c r="J32">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K32" s="1">
         <v>100</v>
@@ -3031,13 +3031,13 @@
         <v>27</v>
       </c>
       <c r="D37">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="E37">
         <v>0</v>
       </c>
       <c r="F37">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="G37" s="1">
         <v>0</v>
@@ -3049,7 +3049,7 @@
         <v>0</v>
       </c>
       <c r="J37">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="K37" s="1">
         <v>100</v>
@@ -3219,22 +3219,22 @@
         <v>30</v>
       </c>
       <c r="D5">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5">
         <v>3</v>
       </c>
       <c r="G5" s="1">
-        <v>91.2</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="H5" s="1">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="I5" s="2">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -3254,22 +3254,22 @@
         <v>31</v>
       </c>
       <c r="D6">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E6">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F6">
         <v>3</v>
       </c>
       <c r="G6" s="1">
-        <v>92.3</v>
+        <v>92.5</v>
       </c>
       <c r="H6" s="1">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="I6" s="2">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -3324,19 +3324,19 @@
         <v>33</v>
       </c>
       <c r="D8">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E8">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F8">
         <v>12</v>
       </c>
       <c r="G8" s="1">
-        <v>69.2</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="H8" s="1">
-        <v>30.8</v>
+        <v>31.6</v>
       </c>
       <c r="I8" s="2">
         <v>6.3</v>
@@ -3356,10 +3356,10 @@
         <v>25</v>
       </c>
       <c r="D9">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E9">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F9">
         <v>25</v>
@@ -3697,19 +3697,19 @@
         <v>40</v>
       </c>
       <c r="D19">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E19">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F19">
         <v>14</v>
       </c>
       <c r="G19" s="1">
-        <v>65</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="H19" s="1">
-        <v>35</v>
+        <v>35.9</v>
       </c>
       <c r="I19" s="2">
         <v>6</v>
@@ -3729,19 +3729,19 @@
         <v>25</v>
       </c>
       <c r="D20">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E20">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F20">
         <v>14</v>
       </c>
       <c r="G20" s="1">
-        <v>65</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="H20" s="1">
-        <v>35</v>
+        <v>35.9</v>
       </c>
       <c r="I20" s="2">
         <v>6</v>
@@ -4102,13 +4102,13 @@
         <v>47</v>
       </c>
       <c r="D31">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E31">
         <v>0</v>
       </c>
       <c r="F31">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G31" s="1">
         <v>0</v>
@@ -4120,7 +4120,7 @@
         <v>0</v>
       </c>
       <c r="J31">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K31" s="1">
         <v>100</v>
@@ -4134,28 +4134,28 @@
         <v>25</v>
       </c>
       <c r="D32">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E32">
         <v>12</v>
       </c>
       <c r="F32">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G32" s="1">
-        <v>13.2</v>
+        <v>13</v>
       </c>
       <c r="H32" s="1">
-        <v>86.8</v>
+        <v>87</v>
       </c>
       <c r="I32" s="2">
         <v>2</v>
       </c>
       <c r="J32">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K32" s="1">
-        <v>61.5</v>
+        <v>62</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -4297,28 +4297,28 @@
         <v>27</v>
       </c>
       <c r="D37">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="E37">
         <v>462</v>
       </c>
       <c r="F37">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G37" s="1">
-        <v>69.3</v>
+        <v>69.2</v>
       </c>
       <c r="H37" s="1">
-        <v>30.7</v>
+        <v>30.8</v>
       </c>
       <c r="I37" s="2">
         <v>6.2</v>
       </c>
       <c r="J37">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K37" s="1">
-        <v>17.4</v>
+        <v>17.5</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Ciencias Sociales - Estadisticos 20231.xlsx
+++ b/academias/Ciencias Sociales - Estadisticos 20231.xlsx
@@ -929,28 +929,28 @@
         <v>36</v>
       </c>
       <c r="D12">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E12">
         <v>31</v>
       </c>
       <c r="F12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G12" s="1">
-        <v>93.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H12" s="1">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="I12" s="2">
         <v>9.6</v>
       </c>
       <c r="J12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>6.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -996,28 +996,28 @@
         <v>25</v>
       </c>
       <c r="D14">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E14">
         <v>128</v>
       </c>
       <c r="F14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G14" s="1">
-        <v>97.7</v>
+        <v>99.2</v>
       </c>
       <c r="H14" s="1">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="I14" s="2">
         <v>9.300000000000001</v>
       </c>
       <c r="J14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1637,28 +1637,28 @@
         <v>48</v>
       </c>
       <c r="D33">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E33">
         <v>2</v>
       </c>
       <c r="F33">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G33" s="1">
-        <v>14.3</v>
+        <v>16.7</v>
       </c>
       <c r="H33" s="1">
-        <v>85.7</v>
+        <v>83.3</v>
       </c>
       <c r="I33" s="2">
         <v>4.8</v>
       </c>
       <c r="J33">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K33" s="1">
-        <v>14.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -1669,28 +1669,28 @@
         <v>25</v>
       </c>
       <c r="D34">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E34">
         <v>2</v>
       </c>
       <c r="F34">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G34" s="1">
-        <v>14.3</v>
+        <v>16.7</v>
       </c>
       <c r="H34" s="1">
-        <v>85.7</v>
+        <v>83.3</v>
       </c>
       <c r="I34" s="2">
         <v>4.8</v>
       </c>
       <c r="J34">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K34" s="1">
-        <v>14.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -1765,28 +1765,28 @@
         <v>27</v>
       </c>
       <c r="D37">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="E37">
         <v>462</v>
       </c>
       <c r="F37">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="G37" s="1">
-        <v>69.2</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="H37" s="1">
-        <v>30.8</v>
+        <v>30.4</v>
       </c>
       <c r="I37" s="2">
         <v>6.2</v>
       </c>
       <c r="J37">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="K37" s="1">
-        <v>17.5</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -2195,13 +2195,13 @@
         <v>36</v>
       </c>
       <c r="D12">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E12">
         <v>0</v>
       </c>
       <c r="F12">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
@@ -2213,7 +2213,7 @@
         <v>0</v>
       </c>
       <c r="J12">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K12" s="1">
         <v>100</v>
@@ -2262,13 +2262,13 @@
         <v>25</v>
       </c>
       <c r="D14">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
       <c r="F14">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G14" s="1">
         <v>0</v>
@@ -2280,7 +2280,7 @@
         <v>0</v>
       </c>
       <c r="J14">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="K14" s="1">
         <v>100</v>
@@ -2903,13 +2903,13 @@
         <v>48</v>
       </c>
       <c r="D33">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E33">
         <v>0</v>
       </c>
       <c r="F33">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G33" s="1">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="J33">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K33" s="1">
         <v>100</v>
@@ -2935,13 +2935,13 @@
         <v>25</v>
       </c>
       <c r="D34">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E34">
         <v>0</v>
       </c>
       <c r="F34">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G34" s="1">
         <v>0</v>
@@ -2953,7 +2953,7 @@
         <v>0</v>
       </c>
       <c r="J34">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K34" s="1">
         <v>100</v>
@@ -3031,13 +3031,13 @@
         <v>27</v>
       </c>
       <c r="D37">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="E37">
         <v>0</v>
       </c>
       <c r="F37">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="G37" s="1">
         <v>0</v>
@@ -3049,7 +3049,7 @@
         <v>0</v>
       </c>
       <c r="J37">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="K37" s="1">
         <v>100</v>
@@ -3461,28 +3461,28 @@
         <v>36</v>
       </c>
       <c r="D12">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E12">
         <v>31</v>
       </c>
       <c r="F12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G12" s="1">
-        <v>93.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H12" s="1">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="I12" s="2">
         <v>9.6</v>
       </c>
       <c r="J12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>6.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -3528,28 +3528,28 @@
         <v>25</v>
       </c>
       <c r="D14">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E14">
         <v>128</v>
       </c>
       <c r="F14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G14" s="1">
-        <v>97.7</v>
+        <v>99.2</v>
       </c>
       <c r="H14" s="1">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="I14" s="2">
         <v>9.300000000000001</v>
       </c>
       <c r="J14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -4169,28 +4169,28 @@
         <v>48</v>
       </c>
       <c r="D33">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E33">
         <v>2</v>
       </c>
       <c r="F33">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G33" s="1">
-        <v>14.3</v>
+        <v>16.7</v>
       </c>
       <c r="H33" s="1">
-        <v>85.7</v>
+        <v>83.3</v>
       </c>
       <c r="I33" s="2">
         <v>5.3</v>
       </c>
       <c r="J33">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K33" s="1">
-        <v>14.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -4201,28 +4201,28 @@
         <v>25</v>
       </c>
       <c r="D34">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E34">
         <v>2</v>
       </c>
       <c r="F34">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G34" s="1">
-        <v>14.3</v>
+        <v>16.7</v>
       </c>
       <c r="H34" s="1">
-        <v>85.7</v>
+        <v>83.3</v>
       </c>
       <c r="I34" s="2">
         <v>5.3</v>
       </c>
       <c r="J34">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K34" s="1">
-        <v>14.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -4297,28 +4297,28 @@
         <v>27</v>
       </c>
       <c r="D37">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="E37">
         <v>462</v>
       </c>
       <c r="F37">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="G37" s="1">
-        <v>69.2</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="H37" s="1">
-        <v>30.8</v>
+        <v>30.4</v>
       </c>
       <c r="I37" s="2">
         <v>6.2</v>
       </c>
       <c r="J37">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="K37" s="1">
-        <v>17.5</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Ciencias Sociales - Estadisticos 20231.xlsx
+++ b/academias/Ciencias Sociales - Estadisticos 20231.xlsx
@@ -687,22 +687,22 @@
         <v>30</v>
       </c>
       <c r="D5">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E5">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F5">
         <v>3</v>
       </c>
       <c r="G5" s="1">
-        <v>91.40000000000001</v>
+        <v>91.2</v>
       </c>
       <c r="H5" s="1">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I5" s="2">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -792,19 +792,19 @@
         <v>33</v>
       </c>
       <c r="D8">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E8">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F8">
         <v>12</v>
       </c>
       <c r="G8" s="1">
-        <v>68.40000000000001</v>
+        <v>69.2</v>
       </c>
       <c r="H8" s="1">
-        <v>31.6</v>
+        <v>30.8</v>
       </c>
       <c r="I8" s="2">
         <v>6.3</v>
@@ -839,7 +839,7 @@
         <v>14</v>
       </c>
       <c r="I9" s="2">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -964,10 +964,10 @@
         <v>37</v>
       </c>
       <c r="D13">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E13">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -996,10 +996,10 @@
         <v>25</v>
       </c>
       <c r="D14">
+        <v>130</v>
+      </c>
+      <c r="E14">
         <v>129</v>
-      </c>
-      <c r="E14">
-        <v>128</v>
       </c>
       <c r="F14">
         <v>1</v>
@@ -1034,25 +1034,25 @@
         <v>30</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F15">
+        <v>9</v>
+      </c>
+      <c r="G15" s="1">
+        <v>70</v>
+      </c>
+      <c r="H15" s="1">
         <v>30</v>
       </c>
-      <c r="G15" s="1">
-        <v>0</v>
-      </c>
-      <c r="H15" s="1">
-        <v>100</v>
-      </c>
       <c r="I15" s="2">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="J15">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1066,25 +1066,25 @@
         <v>30</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F16">
+        <v>9</v>
+      </c>
+      <c r="G16" s="1">
+        <v>70</v>
+      </c>
+      <c r="H16" s="1">
         <v>30</v>
       </c>
-      <c r="G16" s="1">
-        <v>0</v>
-      </c>
-      <c r="H16" s="1">
-        <v>100</v>
-      </c>
       <c r="I16" s="2">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="J16">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1518,10 +1518,10 @@
         <v>5.9</v>
       </c>
       <c r="J29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K29" s="1">
-        <v>2.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -1538,25 +1538,25 @@
         <v>37</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F30">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="G30" s="1">
-        <v>0</v>
+        <v>43.2</v>
       </c>
       <c r="H30" s="1">
-        <v>100</v>
+        <v>56.8</v>
       </c>
       <c r="I30" s="2">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="J30">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K30" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -1573,25 +1573,25 @@
         <v>19</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F31">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="G31" s="1">
-        <v>0</v>
+        <v>73.7</v>
       </c>
       <c r="H31" s="1">
-        <v>100</v>
+        <v>26.3</v>
       </c>
       <c r="I31" s="2">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="J31">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K31" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -1605,25 +1605,25 @@
         <v>92</v>
       </c>
       <c r="E32">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="F32">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="G32" s="1">
-        <v>13</v>
+        <v>45.7</v>
       </c>
       <c r="H32" s="1">
-        <v>87</v>
+        <v>54.3</v>
       </c>
       <c r="I32" s="2">
-        <v>2</v>
+        <v>6.1</v>
       </c>
       <c r="J32">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="K32" s="1">
-        <v>62</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -1707,25 +1707,25 @@
         <v>26</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F35">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="G35" s="1">
-        <v>0</v>
+        <v>92.3</v>
       </c>
       <c r="H35" s="1">
-        <v>100</v>
+        <v>7.7</v>
       </c>
       <c r="I35" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J35">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K35" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -1739,25 +1739,25 @@
         <v>26</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F36">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="G36" s="1">
-        <v>0</v>
+        <v>92.3</v>
       </c>
       <c r="H36" s="1">
-        <v>100</v>
+        <v>7.7</v>
       </c>
       <c r="I36" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J36">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K36" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -1765,28 +1765,28 @@
         <v>27</v>
       </c>
       <c r="D37">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="E37">
-        <v>462</v>
+        <v>538</v>
       </c>
       <c r="F37">
-        <v>202</v>
+        <v>127</v>
       </c>
       <c r="G37" s="1">
-        <v>69.59999999999999</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="H37" s="1">
-        <v>30.4</v>
+        <v>19.1</v>
       </c>
       <c r="I37" s="2">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="J37">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="K37" s="1">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1854,25 +1854,25 @@
         <v>16</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F2">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>12.5</v>
       </c>
       <c r="I2" s="2">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="J2">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1886,25 +1886,25 @@
         <v>16</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F3">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>12.5</v>
       </c>
       <c r="I3" s="2">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="J3">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1921,25 +1921,25 @@
         <v>27</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F4">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>25.9</v>
       </c>
       <c r="I4" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J4">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1953,28 +1953,28 @@
         <v>30</v>
       </c>
       <c r="D5">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F5">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>5.9</v>
       </c>
       <c r="I5" s="2">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="J5">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1991,25 +1991,25 @@
         <v>40</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F6">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="I6" s="2">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J6">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -2026,25 +2026,25 @@
         <v>39</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F7">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>2.6</v>
       </c>
       <c r="I7" s="2">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J7">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -2058,28 +2058,28 @@
         <v>33</v>
       </c>
       <c r="D8">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F8">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>87.2</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>12.8</v>
       </c>
       <c r="I8" s="2">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="J8">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -2093,25 +2093,25 @@
         <v>179</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>162</v>
       </c>
       <c r="F9">
-        <v>179</v>
+        <v>17</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>90.5</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>9.5</v>
       </c>
       <c r="I9" s="2">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J9">
-        <v>179</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -2128,25 +2128,25 @@
         <v>38</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F10">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I10" s="2">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="J10">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -2163,25 +2163,25 @@
         <v>25</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F11">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="I11" s="2">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="J11">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -2198,25 +2198,25 @@
         <v>31</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F12">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I12" s="2">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J12">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -2230,28 +2230,28 @@
         <v>37</v>
       </c>
       <c r="D13">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F13">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I13" s="2">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="J13">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -2262,28 +2262,28 @@
         <v>25</v>
       </c>
       <c r="D14">
+        <v>130</v>
+      </c>
+      <c r="E14">
         <v>129</v>
       </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
       <c r="F14">
-        <v>129</v>
+        <v>1</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>99.2</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>0.8</v>
       </c>
       <c r="I14" s="2">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="J14">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -2434,25 +2434,25 @@
         <v>39</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F19">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G19" s="1">
-        <v>0</v>
+        <v>61.5</v>
       </c>
       <c r="H19" s="1">
-        <v>100</v>
+        <v>38.5</v>
       </c>
       <c r="I19" s="2">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="J19">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -2466,25 +2466,25 @@
         <v>39</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F20">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G20" s="1">
-        <v>0</v>
+        <v>61.5</v>
       </c>
       <c r="H20" s="1">
-        <v>100</v>
+        <v>38.5</v>
       </c>
       <c r="I20" s="2">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="J20">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -2635,25 +2635,25 @@
         <v>30</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F25">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="G25" s="1">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="H25" s="1">
-        <v>100</v>
+        <v>16.7</v>
       </c>
       <c r="I25" s="2">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="J25">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K25" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -2667,25 +2667,25 @@
         <v>30</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F26">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="G26" s="1">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="H26" s="1">
-        <v>100</v>
+        <v>16.7</v>
       </c>
       <c r="I26" s="2">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="J26">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K26" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -2702,25 +2702,25 @@
         <v>26</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F27">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="G27" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H27" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I27" s="2">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="J27">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K27" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -2734,25 +2734,25 @@
         <v>26</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F28">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="G28" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H28" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I28" s="2">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="J28">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K28" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -2769,25 +2769,25 @@
         <v>36</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F29">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="G29" s="1">
-        <v>0</v>
+        <v>36.1</v>
       </c>
       <c r="H29" s="1">
-        <v>100</v>
+        <v>63.9</v>
       </c>
       <c r="I29" s="2">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="J29">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="K29" s="1">
-        <v>100</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -2804,25 +2804,25 @@
         <v>37</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F30">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="G30" s="1">
-        <v>0</v>
+        <v>37.8</v>
       </c>
       <c r="H30" s="1">
-        <v>100</v>
+        <v>62.2</v>
       </c>
       <c r="I30" s="2">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="J30">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K30" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -2839,25 +2839,25 @@
         <v>19</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F31">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="G31" s="1">
-        <v>0</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="H31" s="1">
-        <v>100</v>
+        <v>31.6</v>
       </c>
       <c r="I31" s="2">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="J31">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K31" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -2871,25 +2871,25 @@
         <v>92</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F32">
-        <v>92</v>
+        <v>52</v>
       </c>
       <c r="G32" s="1">
-        <v>0</v>
+        <v>43.5</v>
       </c>
       <c r="H32" s="1">
-        <v>100</v>
+        <v>56.5</v>
       </c>
       <c r="I32" s="2">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="J32">
-        <v>92</v>
+        <v>1</v>
       </c>
       <c r="K32" s="1">
-        <v>100</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -2906,25 +2906,25 @@
         <v>12</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F33">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G33" s="1">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="H33" s="1">
-        <v>100</v>
+        <v>16.7</v>
       </c>
       <c r="I33" s="2">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="J33">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K33" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -2938,25 +2938,25 @@
         <v>12</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F34">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G34" s="1">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="H34" s="1">
-        <v>100</v>
+        <v>16.7</v>
       </c>
       <c r="I34" s="2">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="J34">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K34" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -2973,25 +2973,25 @@
         <v>26</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F35">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="G35" s="1">
-        <v>0</v>
+        <v>96.2</v>
       </c>
       <c r="H35" s="1">
-        <v>100</v>
+        <v>3.8</v>
       </c>
       <c r="I35" s="2">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J35">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K35" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -3005,25 +3005,25 @@
         <v>26</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F36">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="G36" s="1">
-        <v>0</v>
+        <v>96.2</v>
       </c>
       <c r="H36" s="1">
-        <v>100</v>
+        <v>3.8</v>
       </c>
       <c r="I36" s="2">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J36">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K36" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -3031,28 +3031,28 @@
         <v>27</v>
       </c>
       <c r="D37">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>455</v>
       </c>
       <c r="F37">
-        <v>664</v>
+        <v>210</v>
       </c>
       <c r="G37" s="1">
-        <v>0</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="H37" s="1">
-        <v>100</v>
+        <v>31.6</v>
       </c>
       <c r="I37" s="2">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="J37">
-        <v>664</v>
+        <v>116</v>
       </c>
       <c r="K37" s="1">
-        <v>100</v>
+        <v>17.4</v>
       </c>
     </row>
   </sheetData>
@@ -3187,19 +3187,19 @@
         <v>27</v>
       </c>
       <c r="E4">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G4" s="1">
-        <v>81.5</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="H4" s="1">
-        <v>18.5</v>
+        <v>25.9</v>
       </c>
       <c r="I4" s="2">
-        <v>6.7</v>
+        <v>7.4</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -3219,22 +3219,22 @@
         <v>30</v>
       </c>
       <c r="D5">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E5">
         <v>32</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G5" s="1">
-        <v>91.40000000000001</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="H5" s="1">
-        <v>8.6</v>
+        <v>5.9</v>
       </c>
       <c r="I5" s="2">
-        <v>7.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -3257,19 +3257,19 @@
         <v>40</v>
       </c>
       <c r="E6">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G6" s="1">
-        <v>92.5</v>
+        <v>95</v>
       </c>
       <c r="H6" s="1">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="I6" s="2">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -3292,19 +3292,19 @@
         <v>39</v>
       </c>
       <c r="E7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G7" s="1">
-        <v>94.90000000000001</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="H7" s="1">
-        <v>5.1</v>
+        <v>2.6</v>
       </c>
       <c r="I7" s="2">
-        <v>8.199999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -3324,22 +3324,22 @@
         <v>33</v>
       </c>
       <c r="D8">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E8">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F8">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="G8" s="1">
-        <v>68.40000000000001</v>
+        <v>87.2</v>
       </c>
       <c r="H8" s="1">
-        <v>31.6</v>
+        <v>12.8</v>
       </c>
       <c r="I8" s="2">
-        <v>6.3</v>
+        <v>7.4</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -3359,19 +3359,19 @@
         <v>179</v>
       </c>
       <c r="E9">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="F9">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="G9" s="1">
-        <v>86</v>
+        <v>90.5</v>
       </c>
       <c r="H9" s="1">
-        <v>14</v>
+        <v>9.5</v>
       </c>
       <c r="I9" s="2">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -3406,7 +3406,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="2">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -3441,7 +3441,7 @@
         <v>4</v>
       </c>
       <c r="I11" s="2">
-        <v>9.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -3476,7 +3476,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="2">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -3496,10 +3496,10 @@
         <v>37</v>
       </c>
       <c r="D13">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E13">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -3528,10 +3528,10 @@
         <v>25</v>
       </c>
       <c r="D14">
+        <v>130</v>
+      </c>
+      <c r="E14">
         <v>129</v>
-      </c>
-      <c r="E14">
-        <v>128</v>
       </c>
       <c r="F14">
         <v>1</v>
@@ -3566,25 +3566,25 @@
         <v>30</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F15">
+        <v>9</v>
+      </c>
+      <c r="G15" s="1">
+        <v>70</v>
+      </c>
+      <c r="H15" s="1">
         <v>30</v>
       </c>
-      <c r="G15" s="1">
-        <v>0</v>
-      </c>
-      <c r="H15" s="1">
-        <v>100</v>
-      </c>
       <c r="I15" s="2">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="J15">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -3598,25 +3598,25 @@
         <v>30</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F16">
+        <v>9</v>
+      </c>
+      <c r="G16" s="1">
+        <v>70</v>
+      </c>
+      <c r="H16" s="1">
         <v>30</v>
       </c>
-      <c r="G16" s="1">
-        <v>0</v>
-      </c>
-      <c r="H16" s="1">
-        <v>100</v>
-      </c>
       <c r="I16" s="2">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="J16">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -3700,19 +3700,19 @@
         <v>39</v>
       </c>
       <c r="E19">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F19">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G19" s="1">
-        <v>64.09999999999999</v>
+        <v>61.5</v>
       </c>
       <c r="H19" s="1">
-        <v>35.9</v>
+        <v>38.5</v>
       </c>
       <c r="I19" s="2">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -3732,19 +3732,19 @@
         <v>39</v>
       </c>
       <c r="E20">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F20">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G20" s="1">
-        <v>64.09999999999999</v>
+        <v>61.5</v>
       </c>
       <c r="H20" s="1">
-        <v>35.9</v>
+        <v>38.5</v>
       </c>
       <c r="I20" s="2">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -3913,7 +3913,7 @@
         <v>16.7</v>
       </c>
       <c r="I25" s="2">
-        <v>7.8</v>
+        <v>7.3</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -3945,7 +3945,7 @@
         <v>16.7</v>
       </c>
       <c r="I26" s="2">
-        <v>7.8</v>
+        <v>7.3</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -3968,19 +3968,19 @@
         <v>26</v>
       </c>
       <c r="E27">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27" s="1">
-        <v>96.2</v>
+        <v>100</v>
       </c>
       <c r="H27" s="1">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="I27" s="2">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -4000,19 +4000,19 @@
         <v>26</v>
       </c>
       <c r="E28">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G28" s="1">
-        <v>96.2</v>
+        <v>100</v>
       </c>
       <c r="H28" s="1">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="I28" s="2">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -4035,25 +4035,25 @@
         <v>36</v>
       </c>
       <c r="E29">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F29">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G29" s="1">
-        <v>33.3</v>
+        <v>36.1</v>
       </c>
       <c r="H29" s="1">
-        <v>66.7</v>
+        <v>63.9</v>
       </c>
       <c r="I29" s="2">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="J29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K29" s="1">
-        <v>2.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -4070,25 +4070,25 @@
         <v>37</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F30">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="G30" s="1">
-        <v>0</v>
+        <v>37.8</v>
       </c>
       <c r="H30" s="1">
-        <v>100</v>
+        <v>62.2</v>
       </c>
       <c r="I30" s="2">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="J30">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K30" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -4105,25 +4105,25 @@
         <v>19</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F31">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="G31" s="1">
-        <v>0</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="H31" s="1">
-        <v>100</v>
+        <v>31.6</v>
       </c>
       <c r="I31" s="2">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="J31">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K31" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -4137,25 +4137,25 @@
         <v>92</v>
       </c>
       <c r="E32">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="F32">
-        <v>80</v>
+        <v>52</v>
       </c>
       <c r="G32" s="1">
-        <v>13</v>
+        <v>43.5</v>
       </c>
       <c r="H32" s="1">
-        <v>87</v>
+        <v>56.5</v>
       </c>
       <c r="I32" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J32">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="K32" s="1">
-        <v>62</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -4172,19 +4172,19 @@
         <v>12</v>
       </c>
       <c r="E33">
+        <v>10</v>
+      </c>
+      <c r="F33">
         <v>2</v>
       </c>
-      <c r="F33">
-        <v>10</v>
-      </c>
       <c r="G33" s="1">
+        <v>83.3</v>
+      </c>
+      <c r="H33" s="1">
         <v>16.7</v>
       </c>
-      <c r="H33" s="1">
-        <v>83.3</v>
-      </c>
       <c r="I33" s="2">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="J33">
         <v>0</v>
@@ -4204,19 +4204,19 @@
         <v>12</v>
       </c>
       <c r="E34">
+        <v>10</v>
+      </c>
+      <c r="F34">
         <v>2</v>
       </c>
-      <c r="F34">
-        <v>10</v>
-      </c>
       <c r="G34" s="1">
+        <v>83.3</v>
+      </c>
+      <c r="H34" s="1">
         <v>16.7</v>
       </c>
-      <c r="H34" s="1">
-        <v>83.3</v>
-      </c>
       <c r="I34" s="2">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="J34">
         <v>0</v>
@@ -4239,25 +4239,25 @@
         <v>26</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F35">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="G35" s="1">
-        <v>0</v>
+        <v>96.2</v>
       </c>
       <c r="H35" s="1">
-        <v>100</v>
+        <v>3.8</v>
       </c>
       <c r="I35" s="2">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J35">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K35" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -4271,25 +4271,25 @@
         <v>26</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F36">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="G36" s="1">
-        <v>0</v>
+        <v>96.2</v>
       </c>
       <c r="H36" s="1">
-        <v>100</v>
+        <v>3.8</v>
       </c>
       <c r="I36" s="2">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J36">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K36" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -4297,28 +4297,28 @@
         <v>27</v>
       </c>
       <c r="D37">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="E37">
-        <v>462</v>
+        <v>553</v>
       </c>
       <c r="F37">
-        <v>202</v>
+        <v>112</v>
       </c>
       <c r="G37" s="1">
-        <v>69.59999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="H37" s="1">
-        <v>30.4</v>
+        <v>16.8</v>
       </c>
       <c r="I37" s="2">
-        <v>6.2</v>
+        <v>7.7</v>
       </c>
       <c r="J37">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="K37" s="1">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Ciencias Sociales - Estadisticos 20231.xlsx
+++ b/academias/Ciencias Sociales - Estadisticos 20231.xlsx
@@ -2300,25 +2300,25 @@
         <v>30</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F15">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="H15" s="1">
-        <v>100</v>
+        <v>33.3</v>
       </c>
       <c r="I15" s="2">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="J15">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -2332,25 +2332,25 @@
         <v>30</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F16">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="H16" s="1">
-        <v>100</v>
+        <v>33.3</v>
       </c>
       <c r="I16" s="2">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="J16">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -2501,25 +2501,25 @@
         <v>28</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F21">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="G21" s="1">
-        <v>0</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="H21" s="1">
-        <v>100</v>
+        <v>17.9</v>
       </c>
       <c r="I21" s="2">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="J21">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K21" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -2533,25 +2533,25 @@
         <v>28</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F22">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="G22" s="1">
-        <v>0</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="H22" s="1">
-        <v>100</v>
+        <v>17.9</v>
       </c>
       <c r="I22" s="2">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="J22">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K22" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -2568,25 +2568,25 @@
         <v>33</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F23">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="G23" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H23" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I23" s="2">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="J23">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K23" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -2600,25 +2600,25 @@
         <v>33</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F24">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="G24" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H24" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I24" s="2">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="J24">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K24" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -2784,10 +2784,10 @@
         <v>5.7</v>
       </c>
       <c r="J29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K29" s="1">
-        <v>2.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -2886,10 +2886,10 @@
         <v>5.9</v>
       </c>
       <c r="J32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K32" s="1">
-        <v>1.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -3034,25 +3034,25 @@
         <v>665</v>
       </c>
       <c r="E37">
-        <v>455</v>
+        <v>531</v>
       </c>
       <c r="F37">
-        <v>210</v>
+        <v>134</v>
       </c>
       <c r="G37" s="1">
-        <v>68.40000000000001</v>
+        <v>79.8</v>
       </c>
       <c r="H37" s="1">
-        <v>31.6</v>
+        <v>20.2</v>
       </c>
       <c r="I37" s="2">
-        <v>6.6</v>
+        <v>7.5</v>
       </c>
       <c r="J37">
-        <v>116</v>
+        <v>24</v>
       </c>
       <c r="K37" s="1">
-        <v>17.4</v>
+        <v>3.6</v>
       </c>
     </row>
   </sheetData>
@@ -3566,16 +3566,16 @@
         <v>30</v>
       </c>
       <c r="E15">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G15" s="1">
-        <v>70</v>
+        <v>66.7</v>
       </c>
       <c r="H15" s="1">
-        <v>30</v>
+        <v>33.3</v>
       </c>
       <c r="I15" s="2">
         <v>6.5</v>
@@ -3598,16 +3598,16 @@
         <v>30</v>
       </c>
       <c r="E16">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G16" s="1">
-        <v>70</v>
+        <v>66.7</v>
       </c>
       <c r="H16" s="1">
-        <v>30</v>
+        <v>33.3</v>
       </c>
       <c r="I16" s="2">
         <v>6.5</v>
@@ -3779,7 +3779,7 @@
         <v>17.9</v>
       </c>
       <c r="I21" s="2">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -3811,7 +3811,7 @@
         <v>17.9</v>
       </c>
       <c r="I22" s="2">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -3846,7 +3846,7 @@
         <v>0</v>
       </c>
       <c r="I23" s="2">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -3878,7 +3878,7 @@
         <v>0</v>
       </c>
       <c r="I24" s="2">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -4300,16 +4300,16 @@
         <v>665</v>
       </c>
       <c r="E37">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="F37">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G37" s="1">
-        <v>83.2</v>
+        <v>83</v>
       </c>
       <c r="H37" s="1">
-        <v>16.8</v>
+        <v>17</v>
       </c>
       <c r="I37" s="2">
         <v>7.7</v>

--- a/academias/Ciencias Sociales - Estadisticos 20231.xlsx
+++ b/academias/Ciencias Sociales - Estadisticos 20231.xlsx
@@ -2367,25 +2367,25 @@
         <v>24</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F17">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="H17" s="1">
-        <v>100</v>
+        <v>16.7</v>
       </c>
       <c r="I17" s="2">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="J17">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -2399,25 +2399,25 @@
         <v>24</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F18">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="H18" s="1">
-        <v>100</v>
+        <v>16.7</v>
       </c>
       <c r="I18" s="2">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="J18">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -3034,25 +3034,25 @@
         <v>665</v>
       </c>
       <c r="E37">
-        <v>531</v>
+        <v>551</v>
       </c>
       <c r="F37">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="G37" s="1">
-        <v>79.8</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="H37" s="1">
-        <v>20.2</v>
+        <v>17.1</v>
       </c>
       <c r="I37" s="2">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="J37">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K37" s="1">
-        <v>3.6</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3633,19 +3633,19 @@
         <v>24</v>
       </c>
       <c r="E17">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G17" s="1">
-        <v>87.5</v>
+        <v>83.3</v>
       </c>
       <c r="H17" s="1">
-        <v>12.5</v>
+        <v>16.7</v>
       </c>
       <c r="I17" s="2">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -3665,19 +3665,19 @@
         <v>24</v>
       </c>
       <c r="E18">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G18" s="1">
-        <v>87.5</v>
+        <v>83.3</v>
       </c>
       <c r="H18" s="1">
-        <v>12.5</v>
+        <v>16.7</v>
       </c>
       <c r="I18" s="2">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -4300,19 +4300,19 @@
         <v>665</v>
       </c>
       <c r="E37">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="F37">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G37" s="1">
-        <v>83</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="H37" s="1">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="I37" s="2">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="J37">
         <v>0</v>

--- a/academias/Ciencias Sociales - Estadisticos 20231.xlsx
+++ b/academias/Ciencias Sociales - Estadisticos 20231.xlsx
@@ -1637,22 +1637,22 @@
         <v>48</v>
       </c>
       <c r="D33">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E33">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F33">
         <v>10</v>
       </c>
       <c r="G33" s="1">
-        <v>16.7</v>
+        <v>23.1</v>
       </c>
       <c r="H33" s="1">
-        <v>83.3</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="I33" s="2">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="J33">
         <v>0</v>
@@ -1669,22 +1669,22 @@
         <v>25</v>
       </c>
       <c r="D34">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E34">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F34">
         <v>10</v>
       </c>
       <c r="G34" s="1">
-        <v>16.7</v>
+        <v>23.1</v>
       </c>
       <c r="H34" s="1">
-        <v>83.3</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="I34" s="2">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="J34">
         <v>0</v>
@@ -1765,10 +1765,10 @@
         <v>27</v>
       </c>
       <c r="D37">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="E37">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="F37">
         <v>127</v>
@@ -2903,22 +2903,22 @@
         <v>48</v>
       </c>
       <c r="D33">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E33">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F33">
         <v>2</v>
       </c>
       <c r="G33" s="1">
-        <v>83.3</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="H33" s="1">
-        <v>16.7</v>
+        <v>15.4</v>
       </c>
       <c r="I33" s="2">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J33">
         <v>0</v>
@@ -2935,22 +2935,22 @@
         <v>25</v>
       </c>
       <c r="D34">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E34">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F34">
         <v>2</v>
       </c>
       <c r="G34" s="1">
-        <v>83.3</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="H34" s="1">
-        <v>16.7</v>
+        <v>15.4</v>
       </c>
       <c r="I34" s="2">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J34">
         <v>0</v>
@@ -3031,10 +3031,10 @@
         <v>27</v>
       </c>
       <c r="D37">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="E37">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="F37">
         <v>114</v>
@@ -4169,22 +4169,22 @@
         <v>48</v>
       </c>
       <c r="D33">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E33">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F33">
         <v>2</v>
       </c>
       <c r="G33" s="1">
-        <v>83.3</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="H33" s="1">
-        <v>16.7</v>
+        <v>15.4</v>
       </c>
       <c r="I33" s="2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="J33">
         <v>0</v>
@@ -4201,22 +4201,22 @@
         <v>25</v>
       </c>
       <c r="D34">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E34">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F34">
         <v>2</v>
       </c>
       <c r="G34" s="1">
-        <v>83.3</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="H34" s="1">
-        <v>16.7</v>
+        <v>15.4</v>
       </c>
       <c r="I34" s="2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="J34">
         <v>0</v>
@@ -4297,10 +4297,10 @@
         <v>27</v>
       </c>
       <c r="D37">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="E37">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="F37">
         <v>114</v>

--- a/academias/Ciencias Sociales - Estadisticos 20231.xlsx
+++ b/academias/Ciencias Sociales - Estadisticos 20231.xlsx
@@ -3187,16 +3187,16 @@
         <v>27</v>
       </c>
       <c r="E4">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G4" s="1">
-        <v>74.09999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="H4" s="1">
-        <v>25.9</v>
+        <v>18.5</v>
       </c>
       <c r="I4" s="2">
         <v>7.4</v>
@@ -3222,19 +3222,19 @@
         <v>34</v>
       </c>
       <c r="E5">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G5" s="1">
-        <v>94.09999999999999</v>
+        <v>91.2</v>
       </c>
       <c r="H5" s="1">
-        <v>5.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I5" s="2">
-        <v>8.699999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -3257,16 +3257,16 @@
         <v>40</v>
       </c>
       <c r="E6">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6" s="1">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="H6" s="1">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="I6" s="2">
         <v>8.800000000000001</v>
@@ -3292,19 +3292,19 @@
         <v>39</v>
       </c>
       <c r="E7">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7" s="1">
-        <v>97.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="H7" s="1">
-        <v>2.6</v>
+        <v>5.1</v>
       </c>
       <c r="I7" s="2">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -3327,19 +3327,19 @@
         <v>39</v>
       </c>
       <c r="E8">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G8" s="1">
-        <v>87.2</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="H8" s="1">
-        <v>12.8</v>
+        <v>15.4</v>
       </c>
       <c r="I8" s="2">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -3371,7 +3371,7 @@
         <v>9.5</v>
       </c>
       <c r="I9" s="2">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -3406,7 +3406,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="2">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -3429,19 +3429,19 @@
         <v>25</v>
       </c>
       <c r="E11">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G11" s="1">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="H11" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I11" s="2">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -3476,7 +3476,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="2">
-        <v>9.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -3531,19 +3531,19 @@
         <v>130</v>
       </c>
       <c r="E14">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G14" s="1">
-        <v>99.2</v>
+        <v>98.5</v>
       </c>
       <c r="H14" s="1">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="I14" s="2">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -3566,19 +3566,19 @@
         <v>30</v>
       </c>
       <c r="E15">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F15">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G15" s="1">
-        <v>66.7</v>
+        <v>96.7</v>
       </c>
       <c r="H15" s="1">
-        <v>33.3</v>
+        <v>3.3</v>
       </c>
       <c r="I15" s="2">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -3598,19 +3598,19 @@
         <v>30</v>
       </c>
       <c r="E16">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F16">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G16" s="1">
-        <v>66.7</v>
+        <v>96.7</v>
       </c>
       <c r="H16" s="1">
-        <v>33.3</v>
+        <v>3.3</v>
       </c>
       <c r="I16" s="2">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -3700,19 +3700,19 @@
         <v>39</v>
       </c>
       <c r="E19">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F19">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="G19" s="1">
-        <v>61.5</v>
+        <v>79.5</v>
       </c>
       <c r="H19" s="1">
-        <v>38.5</v>
+        <v>20.5</v>
       </c>
       <c r="I19" s="2">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -3732,19 +3732,19 @@
         <v>39</v>
       </c>
       <c r="E20">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F20">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="G20" s="1">
-        <v>61.5</v>
+        <v>79.5</v>
       </c>
       <c r="H20" s="1">
-        <v>38.5</v>
+        <v>20.5</v>
       </c>
       <c r="I20" s="2">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -3767,19 +3767,19 @@
         <v>28</v>
       </c>
       <c r="E21">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F21">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G21" s="1">
-        <v>82.09999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="H21" s="1">
-        <v>17.9</v>
+        <v>14.3</v>
       </c>
       <c r="I21" s="2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -3799,19 +3799,19 @@
         <v>28</v>
       </c>
       <c r="E22">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F22">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G22" s="1">
-        <v>82.09999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="H22" s="1">
-        <v>17.9</v>
+        <v>14.3</v>
       </c>
       <c r="I22" s="2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -3846,7 +3846,7 @@
         <v>0</v>
       </c>
       <c r="I23" s="2">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -3878,7 +3878,7 @@
         <v>0</v>
       </c>
       <c r="I24" s="2">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -3901,19 +3901,19 @@
         <v>30</v>
       </c>
       <c r="E25">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F25">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G25" s="1">
-        <v>83.3</v>
+        <v>96.7</v>
       </c>
       <c r="H25" s="1">
-        <v>16.7</v>
+        <v>3.3</v>
       </c>
       <c r="I25" s="2">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -3933,19 +3933,19 @@
         <v>30</v>
       </c>
       <c r="E26">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F26">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G26" s="1">
-        <v>83.3</v>
+        <v>96.7</v>
       </c>
       <c r="H26" s="1">
-        <v>16.7</v>
+        <v>3.3</v>
       </c>
       <c r="I26" s="2">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -3968,19 +3968,19 @@
         <v>26</v>
       </c>
       <c r="E27">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" s="1">
-        <v>100</v>
+        <v>96.2</v>
       </c>
       <c r="H27" s="1">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="I27" s="2">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -4000,19 +4000,19 @@
         <v>26</v>
       </c>
       <c r="E28">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" s="1">
-        <v>100</v>
+        <v>96.2</v>
       </c>
       <c r="H28" s="1">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="I28" s="2">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -4184,7 +4184,7 @@
         <v>15.4</v>
       </c>
       <c r="I33" s="2">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J33">
         <v>0</v>
@@ -4216,7 +4216,7 @@
         <v>15.4</v>
       </c>
       <c r="I34" s="2">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J34">
         <v>0</v>
@@ -4251,7 +4251,7 @@
         <v>3.8</v>
       </c>
       <c r="I35" s="2">
-        <v>8.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="J35">
         <v>0</v>
@@ -4283,7 +4283,7 @@
         <v>3.8</v>
       </c>
       <c r="I36" s="2">
-        <v>8.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="J36">
         <v>0</v>
@@ -4300,19 +4300,19 @@
         <v>666</v>
       </c>
       <c r="E37">
-        <v>552</v>
+        <v>571</v>
       </c>
       <c r="F37">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="G37" s="1">
-        <v>82.90000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="H37" s="1">
-        <v>17.1</v>
+        <v>14.3</v>
       </c>
       <c r="I37" s="2">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="J37">
         <v>0</v>

--- a/academias/Ciencias Sociales - Estadisticos 20231.xlsx
+++ b/academias/Ciencias Sociales - Estadisticos 20231.xlsx
@@ -3767,16 +3767,16 @@
         <v>28</v>
       </c>
       <c r="E21">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F21">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G21" s="1">
-        <v>85.7</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="H21" s="1">
-        <v>14.3</v>
+        <v>17.9</v>
       </c>
       <c r="I21" s="2">
         <v>7</v>
@@ -3799,16 +3799,16 @@
         <v>28</v>
       </c>
       <c r="E22">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F22">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G22" s="1">
-        <v>85.7</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="H22" s="1">
-        <v>14.3</v>
+        <v>17.9</v>
       </c>
       <c r="I22" s="2">
         <v>7</v>
@@ -4035,19 +4035,19 @@
         <v>36</v>
       </c>
       <c r="E29">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F29">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G29" s="1">
-        <v>36.1</v>
+        <v>33.3</v>
       </c>
       <c r="H29" s="1">
-        <v>63.9</v>
+        <v>66.7</v>
       </c>
       <c r="I29" s="2">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -4070,19 +4070,19 @@
         <v>37</v>
       </c>
       <c r="E30">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F30">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="G30" s="1">
-        <v>37.8</v>
+        <v>51.4</v>
       </c>
       <c r="H30" s="1">
-        <v>62.2</v>
+        <v>48.6</v>
       </c>
       <c r="I30" s="2">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="J30">
         <v>0</v>
@@ -4117,7 +4117,7 @@
         <v>31.6</v>
       </c>
       <c r="I31" s="2">
-        <v>6.4</v>
+        <v>6.1</v>
       </c>
       <c r="J31">
         <v>0</v>
@@ -4137,19 +4137,19 @@
         <v>92</v>
       </c>
       <c r="E32">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F32">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G32" s="1">
-        <v>43.5</v>
+        <v>47.8</v>
       </c>
       <c r="H32" s="1">
-        <v>56.5</v>
+        <v>52.2</v>
       </c>
       <c r="I32" s="2">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J32">
         <v>0</v>
@@ -4300,16 +4300,16 @@
         <v>666</v>
       </c>
       <c r="E37">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="F37">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="G37" s="1">
-        <v>85.7</v>
+        <v>86.2</v>
       </c>
       <c r="H37" s="1">
-        <v>14.3</v>
+        <v>13.8</v>
       </c>
       <c r="I37" s="2">
         <v>7.7</v>

--- a/academias/Ciencias Sociales - Estadisticos 20231.xlsx
+++ b/academias/Ciencias Sociales - Estadisticos 20231.xlsx
@@ -3429,19 +3429,19 @@
         <v>25</v>
       </c>
       <c r="E11">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G11" s="1">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="H11" s="1">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I11" s="2">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -3511,7 +3511,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="2">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -3531,19 +3531,19 @@
         <v>130</v>
       </c>
       <c r="E14">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G14" s="1">
-        <v>98.5</v>
+        <v>97.7</v>
       </c>
       <c r="H14" s="1">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="I14" s="2">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -3700,19 +3700,19 @@
         <v>39</v>
       </c>
       <c r="E19">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F19">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G19" s="1">
-        <v>79.5</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="H19" s="1">
-        <v>20.5</v>
+        <v>15.4</v>
       </c>
       <c r="I19" s="2">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -3732,19 +3732,19 @@
         <v>39</v>
       </c>
       <c r="E20">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F20">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G20" s="1">
-        <v>79.5</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="H20" s="1">
-        <v>20.5</v>
+        <v>15.4</v>
       </c>
       <c r="I20" s="2">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -4300,16 +4300,16 @@
         <v>666</v>
       </c>
       <c r="E37">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="F37">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G37" s="1">
-        <v>86.2</v>
+        <v>86.3</v>
       </c>
       <c r="H37" s="1">
-        <v>13.8</v>
+        <v>13.7</v>
       </c>
       <c r="I37" s="2">
         <v>7.7</v>

--- a/academias/Ciencias Sociales - Estadisticos 20231.xlsx
+++ b/academias/Ciencias Sociales - Estadisticos 20231.xlsx
@@ -3633,19 +3633,19 @@
         <v>24</v>
       </c>
       <c r="E17">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G17" s="1">
-        <v>83.3</v>
+        <v>87.5</v>
       </c>
       <c r="H17" s="1">
-        <v>16.7</v>
+        <v>12.5</v>
       </c>
       <c r="I17" s="2">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -3665,19 +3665,19 @@
         <v>24</v>
       </c>
       <c r="E18">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G18" s="1">
-        <v>83.3</v>
+        <v>87.5</v>
       </c>
       <c r="H18" s="1">
-        <v>16.7</v>
+        <v>12.5</v>
       </c>
       <c r="I18" s="2">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -3700,16 +3700,16 @@
         <v>39</v>
       </c>
       <c r="E19">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G19" s="1">
-        <v>84.59999999999999</v>
+        <v>87.2</v>
       </c>
       <c r="H19" s="1">
-        <v>15.4</v>
+        <v>12.8</v>
       </c>
       <c r="I19" s="2">
         <v>6.7</v>
@@ -3732,16 +3732,16 @@
         <v>39</v>
       </c>
       <c r="E20">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G20" s="1">
-        <v>84.59999999999999</v>
+        <v>87.2</v>
       </c>
       <c r="H20" s="1">
-        <v>15.4</v>
+        <v>12.8</v>
       </c>
       <c r="I20" s="2">
         <v>6.7</v>
@@ -3834,19 +3834,19 @@
         <v>33</v>
       </c>
       <c r="E23">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G23" s="1">
-        <v>100</v>
+        <v>78.8</v>
       </c>
       <c r="H23" s="1">
-        <v>0</v>
+        <v>21.2</v>
       </c>
       <c r="I23" s="2">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -3866,19 +3866,19 @@
         <v>33</v>
       </c>
       <c r="E24">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G24" s="1">
-        <v>100</v>
+        <v>78.8</v>
       </c>
       <c r="H24" s="1">
-        <v>0</v>
+        <v>21.2</v>
       </c>
       <c r="I24" s="2">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -4300,16 +4300,16 @@
         <v>666</v>
       </c>
       <c r="E37">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="F37">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G37" s="1">
-        <v>86.3</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="H37" s="1">
-        <v>13.7</v>
+        <v>14.4</v>
       </c>
       <c r="I37" s="2">
         <v>7.7</v>

--- a/academias/Ciencias Sociales - Estadisticos 20231.xlsx
+++ b/academias/Ciencias Sociales - Estadisticos 20231.xlsx
@@ -3132,7 +3132,7 @@
         <v>12.5</v>
       </c>
       <c r="I2" s="2">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -3164,7 +3164,7 @@
         <v>12.5</v>
       </c>
       <c r="I3" s="2">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -3199,7 +3199,7 @@
         <v>18.5</v>
       </c>
       <c r="I4" s="2">
-        <v>7.4</v>
+        <v>9.1</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -3234,7 +3234,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="I5" s="2">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -3269,7 +3269,7 @@
         <v>2.5</v>
       </c>
       <c r="I6" s="2">
-        <v>8.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -3304,7 +3304,7 @@
         <v>5.1</v>
       </c>
       <c r="I7" s="2">
-        <v>8.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -3339,7 +3339,7 @@
         <v>15.4</v>
       </c>
       <c r="I8" s="2">
-        <v>7.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -3371,7 +3371,7 @@
         <v>9.5</v>
       </c>
       <c r="I9" s="2">
-        <v>8.1</v>
+        <v>9.5</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -3406,7 +3406,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="2">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -3441,7 +3441,7 @@
         <v>12</v>
       </c>
       <c r="I11" s="2">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -3476,7 +3476,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="2">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -3511,7 +3511,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -3543,7 +3543,7 @@
         <v>2.3</v>
       </c>
       <c r="I14" s="2">
-        <v>9.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -3578,7 +3578,7 @@
         <v>3.3</v>
       </c>
       <c r="I15" s="2">
-        <v>6.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -3610,7 +3610,7 @@
         <v>3.3</v>
       </c>
       <c r="I16" s="2">
-        <v>6.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -3645,7 +3645,7 @@
         <v>12.5</v>
       </c>
       <c r="I17" s="2">
-        <v>7</v>
+        <v>9.4</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -3677,7 +3677,7 @@
         <v>12.5</v>
       </c>
       <c r="I18" s="2">
-        <v>7</v>
+        <v>9.4</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -3712,7 +3712,7 @@
         <v>12.8</v>
       </c>
       <c r="I19" s="2">
-        <v>6.7</v>
+        <v>9.4</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -3744,7 +3744,7 @@
         <v>12.8</v>
       </c>
       <c r="I20" s="2">
-        <v>6.7</v>
+        <v>9.4</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -3779,7 +3779,7 @@
         <v>17.9</v>
       </c>
       <c r="I21" s="2">
-        <v>7</v>
+        <v>9.1</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -3811,7 +3811,7 @@
         <v>17.9</v>
       </c>
       <c r="I22" s="2">
-        <v>7</v>
+        <v>9.1</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -3846,7 +3846,7 @@
         <v>21.2</v>
       </c>
       <c r="I23" s="2">
-        <v>7.3</v>
+        <v>8.9</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -3878,7 +3878,7 @@
         <v>21.2</v>
       </c>
       <c r="I24" s="2">
-        <v>7.3</v>
+        <v>8.9</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -3913,7 +3913,7 @@
         <v>3.3</v>
       </c>
       <c r="I25" s="2">
-        <v>7.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -3945,7 +3945,7 @@
         <v>3.3</v>
       </c>
       <c r="I26" s="2">
-        <v>7.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -3980,7 +3980,7 @@
         <v>3.8</v>
       </c>
       <c r="I27" s="2">
-        <v>8.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -4012,7 +4012,7 @@
         <v>3.8</v>
       </c>
       <c r="I28" s="2">
-        <v>8.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -4047,7 +4047,7 @@
         <v>66.7</v>
       </c>
       <c r="I29" s="2">
-        <v>5.6</v>
+        <v>6.7</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -4082,7 +4082,7 @@
         <v>48.6</v>
       </c>
       <c r="I30" s="2">
-        <v>5.9</v>
+        <v>7.6</v>
       </c>
       <c r="J30">
         <v>0</v>
@@ -4117,7 +4117,7 @@
         <v>31.6</v>
       </c>
       <c r="I31" s="2">
-        <v>6.1</v>
+        <v>8.4</v>
       </c>
       <c r="J31">
         <v>0</v>
@@ -4149,7 +4149,7 @@
         <v>52.2</v>
       </c>
       <c r="I32" s="2">
-        <v>5.9</v>
+        <v>7.6</v>
       </c>
       <c r="J32">
         <v>0</v>
@@ -4184,7 +4184,7 @@
         <v>15.4</v>
       </c>
       <c r="I33" s="2">
-        <v>7.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J33">
         <v>0</v>
@@ -4216,7 +4216,7 @@
         <v>15.4</v>
       </c>
       <c r="I34" s="2">
-        <v>7.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J34">
         <v>0</v>
@@ -4251,7 +4251,7 @@
         <v>3.8</v>
       </c>
       <c r="I35" s="2">
-        <v>8.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J35">
         <v>0</v>
@@ -4283,7 +4283,7 @@
         <v>3.8</v>
       </c>
       <c r="I36" s="2">
-        <v>8.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J36">
         <v>0</v>
@@ -4312,7 +4312,7 @@
         <v>14.4</v>
       </c>
       <c r="I37" s="2">
-        <v>7.7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J37">
         <v>0</v>

--- a/academias/Ciencias Sociales - Estadisticos 20231.xlsx
+++ b/academias/Ciencias Sociales - Estadisticos 20231.xlsx
@@ -3132,7 +3132,7 @@
         <v>12.5</v>
       </c>
       <c r="I2" s="2">
-        <v>9.4</v>
+        <v>7.6</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -3164,7 +3164,7 @@
         <v>12.5</v>
       </c>
       <c r="I3" s="2">
-        <v>9.4</v>
+        <v>7.6</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -3199,7 +3199,7 @@
         <v>18.5</v>
       </c>
       <c r="I4" s="2">
-        <v>9.1</v>
+        <v>7.4</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -3234,7 +3234,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="I5" s="2">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -3269,7 +3269,7 @@
         <v>2.5</v>
       </c>
       <c r="I6" s="2">
-        <v>9.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -3304,7 +3304,7 @@
         <v>5.1</v>
       </c>
       <c r="I7" s="2">
-        <v>9.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -3339,7 +3339,7 @@
         <v>15.4</v>
       </c>
       <c r="I8" s="2">
-        <v>9.199999999999999</v>
+        <v>7.3</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -3371,7 +3371,7 @@
         <v>9.5</v>
       </c>
       <c r="I9" s="2">
-        <v>9.5</v>
+        <v>8.1</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -3406,7 +3406,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="2">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -3441,7 +3441,7 @@
         <v>12</v>
       </c>
       <c r="I11" s="2">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -3476,7 +3476,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="2">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -3511,7 +3511,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -3543,7 +3543,7 @@
         <v>2.3</v>
       </c>
       <c r="I14" s="2">
-        <v>9.800000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -3578,7 +3578,7 @@
         <v>3.3</v>
       </c>
       <c r="I15" s="2">
-        <v>9.800000000000001</v>
+        <v>6.7</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -3610,7 +3610,7 @@
         <v>3.3</v>
       </c>
       <c r="I16" s="2">
-        <v>9.800000000000001</v>
+        <v>6.7</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -3645,7 +3645,7 @@
         <v>12.5</v>
       </c>
       <c r="I17" s="2">
-        <v>9.4</v>
+        <v>7</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -3677,7 +3677,7 @@
         <v>12.5</v>
       </c>
       <c r="I18" s="2">
-        <v>9.4</v>
+        <v>7</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -3712,7 +3712,7 @@
         <v>12.8</v>
       </c>
       <c r="I19" s="2">
-        <v>9.4</v>
+        <v>6.7</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -3744,7 +3744,7 @@
         <v>12.8</v>
       </c>
       <c r="I20" s="2">
-        <v>9.4</v>
+        <v>6.7</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -3779,7 +3779,7 @@
         <v>17.9</v>
       </c>
       <c r="I21" s="2">
-        <v>9.1</v>
+        <v>7</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -3811,7 +3811,7 @@
         <v>17.9</v>
       </c>
       <c r="I22" s="2">
-        <v>9.1</v>
+        <v>7</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -3846,7 +3846,7 @@
         <v>21.2</v>
       </c>
       <c r="I23" s="2">
-        <v>8.9</v>
+        <v>7.3</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -3878,7 +3878,7 @@
         <v>21.2</v>
       </c>
       <c r="I24" s="2">
-        <v>8.9</v>
+        <v>7.3</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -3913,7 +3913,7 @@
         <v>3.3</v>
       </c>
       <c r="I25" s="2">
-        <v>9.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -3945,7 +3945,7 @@
         <v>3.3</v>
       </c>
       <c r="I26" s="2">
-        <v>9.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -3980,7 +3980,7 @@
         <v>3.8</v>
       </c>
       <c r="I27" s="2">
-        <v>9.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -4012,7 +4012,7 @@
         <v>3.8</v>
       </c>
       <c r="I28" s="2">
-        <v>9.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -4047,7 +4047,7 @@
         <v>66.7</v>
       </c>
       <c r="I29" s="2">
-        <v>6.7</v>
+        <v>5.6</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -4082,7 +4082,7 @@
         <v>48.6</v>
       </c>
       <c r="I30" s="2">
-        <v>7.6</v>
+        <v>5.9</v>
       </c>
       <c r="J30">
         <v>0</v>
@@ -4117,7 +4117,7 @@
         <v>31.6</v>
       </c>
       <c r="I31" s="2">
-        <v>8.4</v>
+        <v>6.1</v>
       </c>
       <c r="J31">
         <v>0</v>
@@ -4149,7 +4149,7 @@
         <v>52.2</v>
       </c>
       <c r="I32" s="2">
-        <v>7.6</v>
+        <v>5.9</v>
       </c>
       <c r="J32">
         <v>0</v>
@@ -4184,7 +4184,7 @@
         <v>15.4</v>
       </c>
       <c r="I33" s="2">
-        <v>9.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="J33">
         <v>0</v>
@@ -4216,7 +4216,7 @@
         <v>15.4</v>
       </c>
       <c r="I34" s="2">
-        <v>9.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="J34">
         <v>0</v>
@@ -4251,7 +4251,7 @@
         <v>3.8</v>
       </c>
       <c r="I35" s="2">
-        <v>9.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="J35">
         <v>0</v>
@@ -4283,7 +4283,7 @@
         <v>3.8</v>
       </c>
       <c r="I36" s="2">
-        <v>9.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="J36">
         <v>0</v>
@@ -4312,7 +4312,7 @@
         <v>14.4</v>
       </c>
       <c r="I37" s="2">
-        <v>9.300000000000001</v>
+        <v>7.7</v>
       </c>
       <c r="J37">
         <v>0</v>
